--- a/AtchisonRegime/Outputs/Euro/df_regCLI_Euro.xlsx
+++ b/AtchisonRegime/Outputs/Euro/df_regCLI_Euro.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H726"/>
+  <dimension ref="A1:H727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19045,22 +19045,22 @@
         <v>45443</v>
       </c>
       <c r="B716" t="n">
-        <v>100.0515</v>
+        <v>99.94771</v>
       </c>
       <c r="C716" t="n">
-        <v>99.94660666666668</v>
+        <v>99.91201000000001</v>
       </c>
       <c r="D716" t="n">
-        <v>99.8984475</v>
+        <v>99.89556444444445</v>
       </c>
       <c r="E716" t="n">
-        <v>1.454666897301547</v>
+        <v>1.454457727790039</v>
       </c>
       <c r="F716" t="b">
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>0.07440878746934976</v>
+        <v>0.003059559528599793</v>
       </c>
       <c r="H716" t="b">
         <v>1</v>
@@ -19071,22 +19071,22 @@
         <v>45473</v>
       </c>
       <c r="B717" t="n">
-        <v>100.1605</v>
+        <v>100.0449</v>
       </c>
       <c r="C717" t="n">
-        <v>100.0517533333333</v>
+        <v>99.97862333333335</v>
       </c>
       <c r="D717" t="n">
-        <v>99.83926694444443</v>
+        <v>99.83317277777778</v>
       </c>
       <c r="E717" t="n">
-        <v>1.396733252450779</v>
+        <v>1.395755878699208</v>
       </c>
       <c r="F717" t="b">
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0.0780392389232072</v>
+        <v>0.06963252061712617</v>
       </c>
       <c r="H717" t="b">
         <v>1</v>
@@ -19097,22 +19097,22 @@
         <v>45504</v>
       </c>
       <c r="B718" t="n">
-        <v>100.2573</v>
+        <v>100.1276</v>
       </c>
       <c r="C718" t="n">
-        <v>100.1564333333333</v>
+        <v>100.04007</v>
       </c>
       <c r="D718" t="n">
-        <v>99.77628916666667</v>
+        <v>99.76659222222222</v>
       </c>
       <c r="E718" t="n">
-        <v>1.321273456098555</v>
+        <v>1.318750109446916</v>
       </c>
       <c r="F718" t="b">
         <v>1</v>
       </c>
       <c r="G718" t="n">
-        <v>0.07326265395948543</v>
+        <v>0.06271089526937522</v>
       </c>
       <c r="H718" t="b">
         <v>1</v>
@@ -19123,22 +19123,22 @@
         <v>45535</v>
       </c>
       <c r="B719" t="n">
-        <v>100.3287</v>
+        <v>100.1852</v>
       </c>
       <c r="C719" t="n">
-        <v>100.2488333333333</v>
+        <v>100.1192333333333</v>
       </c>
       <c r="D719" t="n">
-        <v>99.71282805555556</v>
+        <v>99.69914499999999</v>
       </c>
       <c r="E719" t="n">
-        <v>1.233036531825402</v>
+        <v>1.227963278768042</v>
       </c>
       <c r="F719" t="b">
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0.05790582692168544</v>
+        <v>0.04690694013080018</v>
       </c>
       <c r="H719" t="b">
         <v>1</v>
@@ -19149,22 +19149,22 @@
         <v>45565</v>
       </c>
       <c r="B720" t="n">
-        <v>100.27</v>
+        <v>100.2196</v>
       </c>
       <c r="C720" t="n">
-        <v>100.2853333333333</v>
+        <v>100.1774666666667</v>
       </c>
       <c r="D720" t="n">
-        <v>99.64841138888889</v>
+        <v>99.63332833333334</v>
       </c>
       <c r="E720" t="n">
-        <v>1.135177284835497</v>
+        <v>1.128082430702608</v>
       </c>
       <c r="F720" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>-0.05170998467301801</v>
+        <v>0.03049422547834524</v>
       </c>
       <c r="H720" t="b">
         <v>1</v>
@@ -19175,22 +19175,22 @@
         <v>45596</v>
       </c>
       <c r="B721" t="n">
-        <v>100.29</v>
+        <v>100.2427</v>
       </c>
       <c r="C721" t="n">
-        <v>100.2962333333333</v>
+        <v>100.2158333333333</v>
       </c>
       <c r="D721" t="n">
-        <v>99.58775861111111</v>
+        <v>99.57136166666666</v>
       </c>
       <c r="E721" t="n">
-        <v>1.033717788584032</v>
+        <v>1.024088060640108</v>
       </c>
       <c r="F721" t="b">
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0.01934764035298829</v>
+        <v>0.02255665395177126</v>
       </c>
       <c r="H721" t="b">
         <v>1</v>
@@ -19201,22 +19201,22 @@
         <v>45626</v>
       </c>
       <c r="B722" t="n">
-        <v>100.32</v>
+        <v>100.2683</v>
       </c>
       <c r="C722" t="n">
-        <v>100.2933333333333</v>
+        <v>100.2435333333333</v>
       </c>
       <c r="D722" t="n">
-        <v>99.53348638888889</v>
+        <v>99.51565333333333</v>
       </c>
       <c r="E722" t="n">
-        <v>0.9352670873869914</v>
+        <v>0.922377355232454</v>
       </c>
       <c r="F722" t="b">
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>0.03207639871494124</v>
+        <v>0.02775436740155613</v>
       </c>
       <c r="H722" t="b">
         <v>1</v>
@@ -19227,22 +19227,22 @@
         <v>45657</v>
       </c>
       <c r="B723" t="n">
-        <v>100.36</v>
+        <v>100.3063</v>
       </c>
       <c r="C723" t="n">
-        <v>100.3233333333333</v>
+        <v>100.2724333333333</v>
       </c>
       <c r="D723" t="n">
-        <v>99.48848361111112</v>
+        <v>99.4691588888889</v>
       </c>
       <c r="E723" t="n">
-        <v>0.849195517672497</v>
+        <v>0.8323993181186224</v>
       </c>
       <c r="F723" t="b">
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>0.04710340453708419</v>
+        <v>0.04565116666107294</v>
       </c>
       <c r="H723" t="b">
         <v>1</v>
@@ -19253,22 +19253,22 @@
         <v>45688</v>
       </c>
       <c r="B724" t="n">
-        <v>100.43</v>
+        <v>100.3653</v>
       </c>
       <c r="C724" t="n">
-        <v>100.37</v>
+        <v>100.3133</v>
       </c>
       <c r="D724" t="n">
-        <v>99.45659749999999</v>
+        <v>99.43547555555556</v>
       </c>
       <c r="E724" t="n">
-        <v>0.7878333063476156</v>
+        <v>0.7665607286628745</v>
       </c>
       <c r="F724" t="b">
         <v>1</v>
       </c>
       <c r="G724" t="n">
-        <v>0.08885128292497106</v>
+        <v>0.07696715706128913</v>
       </c>
       <c r="H724" t="b">
         <v>1</v>
@@ -19279,22 +19279,22 @@
         <v>45716</v>
       </c>
       <c r="B725" t="n">
-        <v>100.53</v>
+        <v>100.4427</v>
       </c>
       <c r="C725" t="n">
-        <v>100.44</v>
+        <v>100.3714333333333</v>
       </c>
       <c r="D725" t="n">
-        <v>99.44151694444444</v>
+        <v>99.41797</v>
       </c>
       <c r="E725" t="n">
-        <v>0.7607405803850509</v>
+        <v>0.7346300827062866</v>
       </c>
       <c r="F725" t="b">
         <v>1</v>
       </c>
       <c r="G725" t="n">
-        <v>0.1314508553617306</v>
+        <v>0.1053591485320955</v>
       </c>
       <c r="H725" t="b">
         <v>1</v>
@@ -19305,24 +19305,50 @@
         <v>45747</v>
       </c>
       <c r="B726" t="n">
-        <v>100.65</v>
+        <v>100.5086</v>
       </c>
       <c r="C726" t="n">
-        <v>100.5366666666667</v>
+        <v>100.4388666666667</v>
       </c>
       <c r="D726" t="n">
-        <v>99.44551138888889</v>
+        <v>99.41803666666667</v>
       </c>
       <c r="E726" t="n">
-        <v>0.7668437158383541</v>
+        <v>0.7347317615214912</v>
       </c>
       <c r="F726" t="b">
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>0.1564856013311842</v>
+        <v>0.08969259728684205</v>
       </c>
       <c r="H726" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B727" t="n">
+        <v>100.5614</v>
+      </c>
+      <c r="C727" t="n">
+        <v>100.5042333333333</v>
+      </c>
+      <c r="D727" t="n">
+        <v>99.43493611111111</v>
+      </c>
+      <c r="E727" t="n">
+        <v>0.7541289755103874</v>
+      </c>
+      <c r="F727" t="b">
+        <v>1</v>
+      </c>
+      <c r="G727" t="n">
+        <v>0.07001454885654049</v>
+      </c>
+      <c r="H727" t="b">
         <v>1</v>
       </c>
     </row>
